--- a/artfynd/A 42274-2025 artfynd.xlsx
+++ b/artfynd/A 42274-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,69 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79394171</v>
+        <v>69694592</v>
       </c>
       <c r="B2" t="n">
-        <v>96232</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219795</v>
+        <v>1467</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bäck VNV Graipesvare, Ås lm</t>
+          <t>Övre Selet, Ö stranden strax V om vägen mellan Grundfors och Ransaren, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502765.9688714592</v>
+        <v>503422</v>
       </c>
       <c r="R2" t="n">
-        <v>7225786.813713306</v>
+        <v>7227616</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>20:55</t>
+          <t>2017-07-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Vid bäcken på uppströmssidan av vägbanken.</t>
+          <t>2017-07-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,77 +754,71 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>björk</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Uno Unger</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Uno Unger, Erik Ljungstrand, Eva Andersson, Stig Ingvarsson</t>
+          <t>Martin Westberg, Måns Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106632570</v>
+        <v>915043</v>
       </c>
       <c r="B3" t="n">
-        <v>56812</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102999</v>
+        <v>2082</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nedre Selet, vid vägen mot Ransarluspen, Ås lm</t>
+          <t>Väg från Ransaren mot Saxnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503161.0377326121</v>
+        <v>503348</v>
       </c>
       <c r="R3" t="n">
-        <v>7226548.49005965</v>
+        <v>7227208</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,22 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:41</t>
+          <t>2000-08-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:04</t>
+          <t>2000-08-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Vägkant och skog väst om väg, låga örter.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,15 +867,2131 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Peter Näslund</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>915700</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100387</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Väg från Ransaren mot Saxnäs, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>503152</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7226441</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2000-08-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2000-08-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Liten bäckravin</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Peter Näslund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>915705</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100387</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Väg från Ransaren mot Saxnäs, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>503077</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7226168</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2000-08-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2000-08-13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Tre små bäckar passerar väg, blöt mark.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Peter Näslund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>915709</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100387</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Väg från Ransaren mot Saxnäs, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>503011</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7226068</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2000-08-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2000-08-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ängsbjörkskog, Bäckstråk</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Peter Näslund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>915712</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100387</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Väg från Ransaren mot Saxnäs, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>502814</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7225829</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2000-08-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2000-08-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera bäckar passerar, blöt skog. Högre örter.Vid bäckstråk.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Peter Näslund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>917062</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100387</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Väg från Ransaren mot Saxnäs, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>502055</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7224051</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2000-08-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2000-08-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Mot sjökant</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Peter Näslund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>917065</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100387</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Väg från Ransaren mot Saxnäs, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>502066</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7223918</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2000-08-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2000-08-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Mot sjökant</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Peter Näslund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>917067</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100387</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Väg från Ransaren mot Saxnäs, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>502098</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7223597</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2000-08-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2000-08-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mot sjökant</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Peter Näslund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>917068</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100387</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Väg från Ransaren mot Saxnäs, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>502096</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7223431</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2000-08-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2000-08-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Från. Mot sjökant till och med vändzon för ej anhörig trafik, nedkommande från bäckraviner.Vid bäckstråk.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Peter Näslund</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>917069</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100387</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Väg från Ransaren mot Saxnäs, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>502728</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7222285</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2000-08-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2000-08-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Till.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Peter Näslund</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>110151018</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Grundfors 164, Vilhelmina, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>502221</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7222871</v>
+      </c>
+      <c r="S13" t="n">
+        <v>6</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bengt Neiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bengt Neiss</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>110151019</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Grundfors 164, Vilhelmina, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>502222</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7222868</v>
+      </c>
+      <c r="S14" t="n">
+        <v>24</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anders Grönvall</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anders Grönvall, Martin Dribe</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>106632570</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58393</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nedre Selet, vid vägen mot Ransarluspen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>503161</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7226548</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Joakim Ekman</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131597486</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58079</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Grundfors, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>502264</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7222740</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134231466</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58596</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gikasjön, Grundfors, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>502695</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7222296</v>
+      </c>
+      <c r="S17" t="n">
+        <v>14</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elias Ernvik</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Elias Ernvik</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>106632569</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nedre Selet, vid vägen mot Ransarluspen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>503161</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7226548</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joakim Ekman, Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>106632642</v>
+      </c>
+      <c r="B19" t="n">
+        <v>29420</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103267</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fjällhumla</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Bombus balteatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Dahlbom, 1832</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>arbetare</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nedre Selet, vid vägen mot Ransarluspen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>503148</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7226468</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Vägskärning, grusväg</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joakim Ekman, Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>106632562</v>
+      </c>
+      <c r="B20" t="n">
+        <v>29437</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103274</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lapphumla</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Bombus lapponicus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1793)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nedre Selet, vid vägen mot Ransarluspen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>503148</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7226468</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Vägskärning, grusväg</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joakim Ekman, Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>79394171</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99017</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bäck VNV Graipesvare, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>502766</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7225787</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2019-08-10</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2019-08-10</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Vid bäcken på uppströmssidan av vägbanken.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Uno Unger</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Uno Unger, Erik Ljungstrand, Eva Andersson, Stig Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>106698163</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99121</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>223614</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vanlig brudsporre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea subsp. conopsea</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Nedre Selet, vid vägen mot Ransarluspen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>503147</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7226464</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Vägskärning, grusväg</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joakim Ekman, Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
